--- a/accountant_forms/030_pass_through_entity_tax_election_form--accountant_forms.xlsx
+++ b/accountant_forms/030_pass_through_entity_tax_election_form--accountant_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SD</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>vt</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>VT</t>
         </is>
       </c>
     </row>
@@ -1295,180 +1295,95 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>tn</t>
+          <t>wy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>WY</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>tax_year_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>tn</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>2018</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>tax_year_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>tx</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>2019</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>tax_year_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>vt</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>2020</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>tax_year_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>wi</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>WI</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>tax_year_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wy</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>tax_year_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>tax_year_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>tax_year_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>tax_year_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>tax_year_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
